--- a/Documents/clientfiles/JO Tool - Roles.xlsx
+++ b/Documents/clientfiles/JO Tool - Roles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gsvictoria\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\clientfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DBE0B80-C494-463E-BD1E-9E3C504FD135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300D175A-57C0-46B0-8450-362979194019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{6030C8BC-A4E0-4BD9-B362-31403DBF26B2}"/>
+    <workbookView xWindow="2256" yWindow="2364" windowWidth="21300" windowHeight="12168" xr2:uid="{6030C8BC-A4E0-4BD9-B362-31403DBF26B2}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -619,18 +619,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E4837C3-94C7-4872-B545-B48A5E914F26}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.90625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="41.90625" customWidth="1"/>
-    <col min="4" max="4" width="39.453125" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" customWidth="1"/>
-    <col min="6" max="6" width="31.08984375" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="59.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -650,7 +652,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -669,8 +671,12 @@
       <c r="F2" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H2" t="str">
+        <f>",'"&amp;B2&amp;"'"</f>
+        <v>,'TA Partner'</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -687,8 +693,12 @@
         <v>35</v>
       </c>
       <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H10" si="0">",'"&amp;B3&amp;"'"</f>
+        <v>,'TA Lead'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -705,8 +715,12 @@
         <v>36</v>
       </c>
       <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>,'PE Head'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -723,8 +737,12 @@
         <v>37</v>
       </c>
       <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>,'HROD Head Approver'</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -741,8 +759,13 @@
         <v>38</v>
       </c>
       <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:6" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>,'Division Head Approver
+(Level 1)'</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -759,8 +782,13 @@
         <v>38</v>
       </c>
       <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>,'Division Head Approver
+(Level 2,3)'</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -777,8 +805,12 @@
         <v>39</v>
       </c>
       <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:6" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>,'Business Admin'</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -797,8 +829,12 @@
       <c r="F9" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>,'System Admin'</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -813,6 +849,10 @@
         <v>48</v>
       </c>
       <c r="F10" s="1"/>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>,'Onboarding Partner'</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -822,12 +862,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B235995-49E9-4741-A461-F2DFC316FEF0}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.81640625" customWidth="1"/>
+    <col min="1" max="1" width="33.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>26</v>
       </c>
@@ -835,7 +875,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -843,7 +883,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -851,7 +891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -865,6 +905,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E905CC0FB92AAA4DB52D2F535F34E1A4" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7bad061a8825ea9617a7c961fc07043e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2b589191-c6d3-45d0-95e2-4cff73607ad1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1909b04aa68677c3b4b49f76a278a155" ns2:_="">
     <xsd:import namespace="2b589191-c6d3-45d0-95e2-4cff73607ad1"/>
@@ -1002,7 +1048,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1011,20 +1057,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50685B82-6E4F-44F6-963A-8843734EB1B4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF011371-0260-4BE2-8CED-D3870430277A}"/>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF011371-0260-4BE2-8CED-D3870430277A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2b589191-c6d3-45d0-95e2-4cff73607ad1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CF8CBB2-3F3E-41FC-BC60-C5688396633C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50685B82-6E4F-44F6-963A-8843734EB1B4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CF8CBB2-3F3E-41FC-BC60-C5688396633C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>